--- a/nr-valueset-ruleset/ig/CodeSystem-fr-core-cs-type-activite.xlsx
+++ b/nr-valueset-ruleset/ig/CodeSystem-fr-core-cs-type-activite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:51:45+00:00</t>
+    <t>2026-02-03T14:58:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-valueset-ruleset/ig/CodeSystem-fr-core-cs-type-activite.xlsx
+++ b/nr-valueset-ruleset/ig/CodeSystem-fr-core-cs-type-activite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T14:58:38+00:00</t>
+    <t>2026-02-17T13:17:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-valueset-ruleset/ig/CodeSystem-fr-core-cs-type-activite.xlsx
+++ b/nr-valueset-ruleset/ig/CodeSystem-fr-core-cs-type-activite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T13:17:39+00:00</t>
+    <t>2026-02-17T14:34:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-valueset-ruleset/ig/CodeSystem-fr-core-cs-type-activite.xlsx
+++ b/nr-valueset-ruleset/ig/CodeSystem-fr-core-cs-type-activite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T14:34:23+00:00</t>
+    <t>2026-02-22T17:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-valueset-ruleset/ig/CodeSystem-fr-core-cs-type-activite.xlsx
+++ b/nr-valueset-ruleset/ig/CodeSystem-fr-core-cs-type-activite.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="116">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T17:13:24+00:00</t>
+    <t>2026-02-22T17:25:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -705,7 +705,9 @@
       <c r="C2" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -717,7 +719,9 @@
       <c r="C3" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -729,7 +733,9 @@
       <c r="C4" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>48</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
@@ -741,7 +747,9 @@
       <c r="C5" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>50</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
@@ -753,7 +761,9 @@
       <c r="C6" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>52</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
@@ -765,7 +775,9 @@
       <c r="C7" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>54</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
@@ -777,7 +789,9 @@
       <c r="C8" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>56</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
@@ -789,7 +803,9 @@
       <c r="C9" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>58</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
@@ -801,7 +817,9 @@
       <c r="C10" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>60</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
@@ -813,7 +831,9 @@
       <c r="C11" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>62</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
@@ -825,7 +845,9 @@
       <c r="C12" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="D12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>64</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
@@ -837,7 +859,9 @@
       <c r="C13" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="D13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>66</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
@@ -849,7 +873,9 @@
       <c r="C14" t="s" s="2">
         <v>68</v>
       </c>
-      <c r="D14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>68</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
@@ -861,7 +887,9 @@
       <c r="C15" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="D15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>70</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
@@ -873,7 +901,9 @@
       <c r="C16" t="s" s="2">
         <v>72</v>
       </c>
-      <c r="D16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>72</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
@@ -885,7 +915,9 @@
       <c r="C17" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="D17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>74</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
@@ -897,7 +929,9 @@
       <c r="C18" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="D18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>76</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
@@ -909,7 +943,9 @@
       <c r="C19" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="D19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
@@ -921,7 +957,9 @@
       <c r="C20" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="D20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>80</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
@@ -933,7 +971,9 @@
       <c r="C21" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="D21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>82</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
@@ -945,7 +985,9 @@
       <c r="C22" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="D22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>84</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
@@ -957,7 +999,9 @@
       <c r="C23" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="D23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>86</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
@@ -969,7 +1013,9 @@
       <c r="C24" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="D24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>88</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
@@ -981,7 +1027,9 @@
       <c r="C25" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="D25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>90</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
@@ -993,7 +1041,9 @@
       <c r="C26" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="D26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>92</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
@@ -1005,7 +1055,9 @@
       <c r="C27" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="D27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>94</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
@@ -1017,7 +1069,9 @@
       <c r="C28" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="D28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>96</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
@@ -1029,7 +1083,9 @@
       <c r="C29" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="D29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>98</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
@@ -1041,7 +1097,9 @@
       <c r="C30" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="D30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>100</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
@@ -1053,7 +1111,9 @@
       <c r="C31" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="D31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>102</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
@@ -1065,7 +1125,9 @@
       <c r="C32" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="D32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>104</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
@@ -1077,7 +1139,9 @@
       <c r="C33" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="D33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>105</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
@@ -1089,7 +1153,9 @@
       <c r="C34" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="D34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>107</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
@@ -1101,7 +1167,9 @@
       <c r="C35" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="D35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>109</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
@@ -1113,7 +1181,9 @@
       <c r="C36" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="D36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>111</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
@@ -1125,7 +1195,9 @@
       <c r="C37" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="D37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>113</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
@@ -1137,7 +1209,9 @@
       <c r="C38" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="D38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>115</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
